--- a/stories/arbres/ATOM-SEC.RUE.003-03.xlsx
+++ b/stories/arbres/ATOM-SEC.RUE.003-03.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -602,7 +602,6 @@
           <t>secondary_lessons</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -819,6 +818,18 @@
       <c r="B29" t="inlineStr">
         <is>
           <t>xlsx-arbre-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>voice_cast</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>voix-roles-v1</t>
         </is>
       </c>
     </row>
@@ -833,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV6"/>
+  <dimension ref="A1:AW6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1127,6 +1138,11 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1151,7 +1167,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Élise sort avec papa. Ils vont à l'école. La rue sent le pain chaud. Élise reste près de l'adulte. Elle prend la main de papa. Main ou manteau. Les pieds d'Élise marchent à côté. Papa dit : près de moi. Élise sent la main. La main est chaude. Ils passent la boulangerie. Élise reste près de l'adulte. Les pieds restent près. La main tient le manteau. Papa dit : tu marches à côté. Élise hoche la tête. Plus tard, ils vont au marché. La rue sent les oranges. Élise se souvient. Elle reste près de l'adulte. Elle prend la main de papa. Main ou manteau. Les pieds marchent à côté. Papa achète une pomme. Élise garde la main. Même leçon, autre rue. Papa dit : merci d'être près de moi.</t>
+          <t>Élise sort avec papa. Ils vont à l'école. La rue sent le pain chaud. Élise reste près de l'adulte. Elle prend la main de papa. Main ou manteau. Les pieds d'Élise marchent à côté. Près de moi. Élise sent la main. La main est chaude. Ils passent la boulangerie. Élise reste près de l'adulte. Les pieds restent près. La main tient le manteau. Tu marches à côté. Élise hoche la tête. Plus tard, ils vont au marché. La rue sent les oranges. Élise se souvient. Elle reste près de l'adulte. Elle prend la main de papa. Main ou manteau. Les pieds marchent à côté. Papa achète une pomme. Élise garde la main. Même leçon, autre rue. Merci d'être près de moi.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1289,6 +1305,16 @@
         <v>8</v>
       </c>
       <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>narrateur|Élise sort avec papa. Ils vont à l'école. La rue sent le pain chaud. Élise reste près de l'adulte. Elle prend la main de papa. Main ou manteau. Les pieds d'Élise marchent à côté.
+papa|Près de moi.
+narrateur|Élise sent la main. La main est chaude. Ils passent la boulangerie. Élise reste près de l'adulte. Les pieds restent près. La main tient le manteau.
+papa|Tu marches à côté.
+narrateur|Élise hoche la tête. Plus tard, ils vont au marché. La rue sent les oranges. Élise se souvient. Elle reste près de l'adulte. Elle prend la main de papa. Main ou manteau. Les pieds marchent à côté. Papa achète une pomme. Élise garde la main. Même leçon, autre rue.
+papa|Merci d'être près de moi.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1469,6 +1495,11 @@
       <c r="AV3" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>narrateur|Élise marche dans la rue. Où reste-t-elle ?</t>
         </is>
       </c>
     </row>
@@ -1641,6 +1672,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>narrateur|Élise est près de papa. À l'école, puis au marché. Main ou manteau. Les pieds restent à côté.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1807,6 +1843,11 @@
         <v>8</v>
       </c>
       <c r="AV5" s="2" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>narrateur|Élise garde la main de papa. Ils rentrent à la maison.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1969,6 +2010,11 @@
         <v>8</v>
       </c>
       <c r="AV6" s="2" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -1987,7 +2033,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:A3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2004,6 +2050,13 @@
       <c r="A2" t="inlineStr">
         <is>
           <t>conversion structurelle, prompts de choix alignés, TTS profilé</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-SEC.RUE.003-03.xlsx
+++ b/stories/arbres/ATOM-SEC.RUE.003-03.xlsx
@@ -844,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW6"/>
+  <dimension ref="A1:AX6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1143,6 +1143,11 @@
           <t>script</t>
         </is>
       </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1315,6 +1320,7 @@
 papa|Merci d'être près de moi.</t>
         </is>
       </c>
+      <c r="AX2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1502,6 +1508,7 @@
           <t>narrateur|Élise marche dans la rue. Où reste-t-elle ?</t>
         </is>
       </c>
+      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1677,6 +1684,7 @@
           <t>narrateur|Élise est près de papa. À l'école, puis au marché. Main ou manteau. Les pieds restent à côté.</t>
         </is>
       </c>
+      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1848,6 +1856,7 @@
           <t>narrateur|Élise garde la main de papa. Ils rentrent à la maison.</t>
         </is>
       </c>
+      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -2015,6 +2024,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX6" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2033,7 +2043,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2057,6 +2067,20 @@
       <c r="A3" t="inlineStr">
         <is>
           <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
         </is>
       </c>
     </row>
@@ -2071,7 +2095,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -2258,6 +2282,18 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ids de bruits (vide = silence). Le bruit se joue, puis l'histoire reprend au calme.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/stories/arbres/ATOM-SEC.RUE.003-03.xlsx
+++ b/stories/arbres/ATOM-SEC.RUE.003-03.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B30"/>
+  <dimension ref="A1:B31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -544,7 +544,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Élise reste près de papa, deux rues</t>
+          <t>Le pain et le square</t>
         </is>
       </c>
     </row>
@@ -830,6 +830,18 @@
       <c r="B30" t="inlineStr">
         <is>
           <t>voix-roles-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>fil_rouge</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Chouchou veut un pain au lait, puis la balançoire du square. Deux rues. Un vélo sonne, une feuille vole. Elle reste près de papa. Puis le pain tiède et le bois de la balançoire.</t>
         </is>
       </c>
     </row>
@@ -1172,12 +1184,12 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Élise sort avec papa. Ils vont à l'école. La rue sent le pain chaud. Élise reste près de l'adulte. Elle prend la main de papa. Main ou manteau. Les pieds d'Élise marchent à côté. Près de moi. Élise sent la main. La main est chaude. Ils passent la boulangerie. Élise reste près de l'adulte. Les pieds restent près. La main tient le manteau. Tu marches à côté. Élise hoche la tête. Plus tard, ils vont au marché. La rue sent les oranges. Élise se souvient. Elle reste près de l'adulte. Elle prend la main de papa. Main ou manteau. Les pieds marchent à côté. Papa achète une pomme. Élise garde la main. Même leçon, autre rue. Merci d'être près de moi.</t>
+          <t>La farine poudre le seuil de la boulangerie. Elle fait un nuage blanc, tout léger, dès qu'on ouvre. Ça sent le beurre chaud et un peu de vanille. Chouchou vit ici, avec papa. Papa, ça sent le pain au lait ! Oui. Il est encore tiède. Tu as vu la farine sur le seuil ? On dirait de la neige. En ce moment, Chouchou prend la main de papa. La main est chaude, un peu farineuse déjà. Je veux le pain au lait. On y va. Tu restes près de moi. Ils marchent sur le trottoir de la première rue. Un vélo passe, tout près. Sa sonnette fait dring. Il va vite ! Nous, on reste près. Tu tiens ma main ? Oui. Chouchou serre plus fort. Leurs épaules se touchent un instant. Bravo. La clochette de la boulangerie fait ding. Papa glisse le pain au lait dans le sac. Il est chaud à travers le papier ! Oui. Maintenant, le square. Autre rue. Même chose. La deuxième rue sent l'herbe coupée. Le square montre déjà une balançoire rouge. La balançoire ! On y va près l'un de l'autre. Une feuille sèche vole très bas. Elle tapote la chaussure de Chouchou. Elle me chatouille ! Tu restes près de moi ? Près de toi. Chouchou tient le manteau, puis la main. Le sac de pain tape doucement contre la jambe. Tu marches à côté ? À côté. Le bois de la balançoire est plus proche. L'herbe du square brille un peu. Merci d'être restée près. Les deux rues. Chouchou garde encore la main. Le pain au lait parfume le sac.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Élise sort avec papa. Ils vont à l'école. La rue sent le pain chaud. Élise reste &lt;emphasis level="moderate"&gt;près&lt;/emphasis&gt; de l'adulte. Elle prend la main de papa. Main ou manteau. Les pieds d'Élise marchent à côté. Papa dit : près de moi. Élise sent la main. La main est chaude. Ils passent la boulangerie. Élise reste près de l'adulte. Les pieds restent près. La main tient le manteau. Papa dit : tu marches à côté. Élise hoche la tête. Plus tard, ils vont au marché. La rue sent les oranges. Élise se souvient. Elle reste près de l'adulte. Elle prend la main de papa. Main ou manteau. Les pieds marchent à côté. Papa achète une pomme. Élise garde la main. Même leçon, autre rue. Papa dit : merci d'être près de moi.&lt;/prosody&gt;&lt;break time="400ms"/&gt;&lt;/speak&gt;</t>
+          <t>La farine poudre le seuil de la boulangerie. Elle fait un nuage blanc, tout léger, dès qu'on ouvre. Ça sent le beurre chaud et un peu de vanille. Chouchou vit ici, avec papa. Papa, ça sent le pain au lait ! Oui. Il est encore tiède. Tu as vu la farine sur le seuil ? On dirait de la neige. En ce moment, Chouchou prend la main de papa. La main est chaude, un peu farineuse déjà. Je veux le pain au lait. On y va. Tu restes près de moi. Ils marchent sur le trottoir de la première rue. Un vélo passe, tout près. Sa sonnette fait dring. Il va vite ! Nous, on reste près. Tu tiens ma main ? Oui. Chouchou serre plus fort. Leurs épaules se touchent un instant. Bravo. La clochette de la boulangerie fait ding. Papa glisse le pain au lait dans le sac. Il est chaud à travers le papier ! Oui. Maintenant, le square. Autre rue. Même chose. La deuxième rue sent l'herbe coupée. Le square montre déjà une balançoire rouge. La balançoire ! On y va près l'un de l'autre. Une feuille sèche vole très bas. Elle tapote la chaussure de Chouchou. Elle me chatouille ! Tu restes près de moi ? Près de toi. Chouchou tient le manteau, puis la main. Le sac de pain tape doucement contre la jambe. Tu marches à côté ? À côté. Le bois de la balançoire est plus proche. L'herbe du square brille un peu. Merci d'être restée près. Les deux rues. Chouchou garde encore la main. Le pain au lait parfume le sac.</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -1240,7 +1252,7 @@
         <v>0.96</v>
       </c>
       <c r="AB2" s="2" t="n">
-        <v>1.12</v>
+        <v>1.22</v>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
@@ -1312,15 +1324,63 @@
       <c r="AV2" s="2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>narrateur|Élise sort avec papa. Ils vont à l'école. La rue sent le pain chaud. Élise reste près de l'adulte. Elle prend la main de papa. Main ou manteau. Les pieds d'Élise marchent à côté.
-papa|Près de moi.
-narrateur|Élise sent la main. La main est chaude. Ils passent la boulangerie. Élise reste près de l'adulte. Les pieds restent près. La main tient le manteau.
-papa|Tu marches à côté.
-narrateur|Élise hoche la tête. Plus tard, ils vont au marché. La rue sent les oranges. Élise se souvient. Elle reste près de l'adulte. Elle prend la main de papa. Main ou manteau. Les pieds marchent à côté. Papa achète une pomme. Élise garde la main. Même leçon, autre rue.
-papa|Merci d'être près de moi.</t>
-        </is>
-      </c>
-      <c r="AX2" t="inlineStr"/>
+          <t>narrateur|La farine poudre le seuil de la boulangerie.
+narrateur|Elle fait un nuage blanc, tout léger, dès qu'on ouvre.
+narrateur|Ça sent le beurre chaud et un peu de vanille.
+narrateur|Chouchou vit ici, avec papa.
+enfant-f|Papa, ça sent le pain au lait !
+papa|Oui.
+papa|Il est encore tiède.
+papa|Tu as vu la farine sur le seuil ?
+enfant-f|On dirait de la neige.
+narrateur|En ce moment, Chouchou prend la main de papa.
+narrateur|La main est chaude, un peu farineuse déjà.
+enfant-f|Je veux le pain au lait.
+papa|On y va.
+papa|Tu restes près de moi.
+narrateur|Ils marchent sur le trottoir de la première rue.
+narrateur|Un vélo passe, tout près.
+narrateur|Sa sonnette fait dring.
+enfant-f|Il va vite !
+papa|Nous, on reste près.
+papa|Tu tiens ma main ?
+enfant-f|Oui.
+narrateur|Chouchou serre plus fort.
+narrateur|Leurs épaules se touchent un instant.
+papa|Bravo.
+narrateur|La clochette de la boulangerie fait ding.
+narrateur|Papa glisse le pain au lait dans le sac.
+enfant-f|Il est chaud à travers le papier !
+papa|Oui.
+papa|Maintenant, le square.
+papa|Autre rue.
+papa|Même chose.
+narrateur|La deuxième rue sent l'herbe coupée.
+narrateur|Le square montre déjà une balançoire rouge.
+enfant-f|La balançoire !
+papa|On y va près l'un de l'autre.
+narrateur|Une feuille sèche vole très bas.
+narrateur|Elle tapote la chaussure de Chouchou.
+enfant-f|Elle me chatouille !
+papa|Tu restes près de moi ?
+enfant-f|Près de toi.
+narrateur|Chouchou tient le manteau, puis la main.
+narrateur|Le sac de pain tape doucement contre la jambe.
+papa|Tu marches à côté ?
+enfant-f|À côté.
+narrateur|Le bois de la balançoire est plus proche.
+narrateur|L'herbe du square brille un peu.
+papa|Merci d'être restée près.
+papa|Les deux rues.
+narrateur|Chouchou garde encore la main.
+narrateur|Le pain au lait parfume le sac.</t>
+        </is>
+      </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>enfants_parc</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1345,12 +1405,12 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Élise marche dans la rue. Où reste-t-elle ?</t>
+          <t>Chouchou marche dans la rue. Où reste-t-elle ?</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="low"&gt;Élise marche dans la rue. Où reste-t-elle ?&lt;/prosody&gt;&lt;break time="250ms"/&gt;&lt;/speak&gt;</t>
+          <t>Chouchou marche dans la rue. Où reste-t-elle ?</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
@@ -1365,7 +1425,7 @@
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>près de papa | près | la main | manteau | à côté</t>
+          <t>près | près de papa | à côté | la main | le manteau | les deux rues</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
@@ -1380,7 +1440,7 @@
       </c>
       <c r="L3" s="2" t="inlineStr">
         <is>
-          <t>Elle reste près. Elle tient la main. Où est Élise ?</t>
+          <t>Elle reste près de papa. Où reste Chouchou ?</t>
         </is>
       </c>
       <c r="M3" s="2" t="inlineStr"/>
@@ -1429,7 +1489,7 @@
         <v>0.9</v>
       </c>
       <c r="AB3" s="2" t="n">
-        <v>1.24</v>
+        <v>1.28</v>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
@@ -1505,10 +1565,10 @@
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>narrateur|Élise marche dans la rue. Où reste-t-elle ?</t>
-        </is>
-      </c>
-      <c r="AX3" t="inlineStr"/>
+          <t>narrateur|Chouchou marche dans la rue.
+narrateur|Où reste-t-elle ?</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1533,12 +1593,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Élise est près de papa. À l'école, puis au marché. Main ou manteau. Les pieds restent à côté.</t>
+          <t>Chouchou est près de papa. À la boulangerie, puis au square. La main tient le manteau, ou la main. Tu es restée près, dans les deux rues ? Oui. Près de toi. Bravo, Chouchou. Près de moi. Le sac sent encore le beurre chaud. La farine du seuil est loin maintenant. La balançoire rouge attend dans l'herbe.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="low"&gt;Élise est &lt;emphasis level="moderate"&gt;près&lt;/emphasis&gt; de papa. À l'école, puis au marché. Main ou manteau. Les pieds restent à côté.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Chouchou est près de papa. À la boulangerie, puis au square. La main tient le manteau, ou la main. Tu es restée près, dans les deux rues ? Oui. Près de toi. Bravo, Chouchou. Près de moi. Le sac sent encore le beurre chaud. La farine du seuil est loin maintenant. La balançoire rouge attend dans l'herbe.</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -1594,7 +1654,7 @@
       </c>
       <c r="Z4" s="2" t="inlineStr">
         <is>
-          <t>slow</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="AA4" s="2" t="n">
@@ -1681,10 +1741,19 @@
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>narrateur|Élise est près de papa. À l'école, puis au marché. Main ou manteau. Les pieds restent à côté.</t>
-        </is>
-      </c>
-      <c r="AX4" t="inlineStr"/>
+          <t>narrateur|Chouchou est près de papa.
+narrateur|À la boulangerie, puis au square.
+narrateur|La main tient le manteau, ou la main.
+papa|Tu es restée près, dans les deux rues ?
+enfant-f|Oui.
+enfant-f|Près de toi.
+papa|Bravo, Chouchou.
+papa|Près de moi.
+narrateur|Le sac sent encore le beurre chaud.
+narrateur|La farine du seuil est loin maintenant.
+narrateur|La balançoire rouge attend dans l'herbe.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1709,12 +1778,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Élise garde la main de papa. Ils rentrent à la maison.</t>
+          <t>Papa ouvre le sac près du banc. Tu manges un bout ? Chouchou mord le pain au lait, tout tiède. Il est doux ! Oui. Tu es restée près. Une miette tombe dans l'herbe. Un moineau la regarde, la tête de côté. Je peux aller à la balançoire ? On y va ensemble. Chouchou tient encore la main jusqu'au bois. Le siège rouge est un peu rêche, un peu chaud. Pousse tout doux. Je te vois. Tu es restée près, puis ici. Le square sent l'herbe et la vanille. Le pain au lait repose dans le sac ouvert. La sonnette du vélo s'est tue.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="low"&gt;Élise garde la &lt;emphasis level="moderate"&gt;main&lt;/emphasis&gt; de papa. Ils rentrent à la maison.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Papa ouvre le sac près du banc. Tu manges un bout ? Chouchou mord le pain au lait, tout tiède. Il est doux ! Oui. Tu es restée près. Une miette tombe dans l'herbe. Un moineau la regarde, la tête de côté. Je peux aller à la balançoire ? On y va ensemble. Chouchou tient encore la main jusqu'au bois. Le siège rouge est un peu rêche, un peu chaud. Pousse tout doux. Je te vois. Tu es restée près, puis ici. Le square sent l'herbe et la vanille. Le pain au lait repose dans le sac ouvert. La sonnette du vélo s'est tue.</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1770,7 +1839,7 @@
       </c>
       <c r="Z5" s="2" t="inlineStr">
         <is>
-          <t>slow</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="AA5" s="2" t="n">
@@ -1853,10 +1922,26 @@
       <c r="AV5" s="2" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>narrateur|Élise garde la main de papa. Ils rentrent à la maison.</t>
-        </is>
-      </c>
-      <c r="AX5" t="inlineStr"/>
+          <t>narrateur|Papa ouvre le sac près du banc.
+papa|Tu manges un bout ?
+narrateur|Chouchou mord le pain au lait, tout tiède.
+enfant-f|Il est doux !
+papa|Oui.
+papa|Tu es restée près.
+narrateur|Une miette tombe dans l'herbe.
+narrateur|Un moineau la regarde, la tête de côté.
+enfant-f|Je peux aller à la balançoire ?
+papa|On y va ensemble.
+narrateur|Chouchou tient encore la main jusqu'au bois.
+narrateur|Le siège rouge est un peu rêche, un peu chaud.
+enfant-f|Pousse tout doux.
+papa|Je te vois.
+papa|Tu es restée près, puis ici.
+narrateur|Le square sent l'herbe et la vanille.
+narrateur|Le pain au lait repose dans le sac ouvert.
+narrateur|La sonnette du vélo s'est tue.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1881,12 +1966,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Le pain sent encore le four. Oui. Merci d'être restée près. La balançoire se tait, tout doux. Le pain tiède parfume encore le square.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="low"&gt;L'histoire est finie.&lt;/prosody&gt;&lt;break time="600ms"/&gt;&lt;/speak&gt;</t>
+          <t>Le pain sent encore le four. Oui. Merci d'être restée près. La balançoire se tait, tout doux. Le pain tiède parfume encore le square.</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -1942,7 +2027,7 @@
       </c>
       <c r="Z6" s="2" t="inlineStr">
         <is>
-          <t>slow</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="AA6" s="2" t="n">
@@ -2021,10 +2106,13 @@
       <c r="AV6" s="2" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
-        </is>
-      </c>
-      <c r="AX6" t="inlineStr"/>
+          <t>enfant-f|Le pain sent encore le four.
+papa|Oui.
+papa|Merci d'être restée près.
+narrateur|La balançoire se tait, tout doux.
+narrateur|Le pain tiède parfume encore le square.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2043,7 +2131,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:A6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2081,6 +2169,13 @@
       <c r="A5" t="inlineStr">
         <is>
           <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>F-NAR-008 récit, pas une leçon en puces</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-SEC.RUE.003-03.xlsx
+++ b/stories/arbres/ATOM-SEC.RUE.003-03.xlsx
@@ -671,7 +671,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>rue de l'école puis rue du marché</t>
+          <t>rue de la boulangerie puis rue du square, après-midi</t>
         </is>
       </c>
     </row>
@@ -683,7 +683,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Élise, papa</t>
+          <t>Chouchou, papa</t>
         </is>
       </c>
     </row>
